--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>non_confirmee</t>
+          <t>universelle_verifiee</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Martingale, grids, position stacking, going all-in, heavy scalping and reversing after a loss are not banned in themselves on accounts bought since 12 March 2026. They stay bound by the risk limits above.</t>
+          <t>The help centre removed martingale, grids, position stacking, all-in trading and heavy scalping from the banned list for accounts bought since 12 March 2026, and the pricing page says they are allowed. The August 2026 fee document still lists martingale and grids as prohibited on funded accounts. The firm has not reconciled the two.</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>source_conflict</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>Risk review within 24 hours, then one to two working days to pay: one to three working days in total after an eligible request.</t>
+          <t>Risk review within 24 hours, then one to two working days to pay. The firm currently announces 7 to 14 working days while it upgrades its payment infrastructure.</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>One reset per account, requested within seven days of the breach and non-refundable. It returns you to the start of the current phase. Not offered on Instant, Synthetic or scaled accounts.</t>
+          <t>One reset per account, requested within seven days of the breach and non-refundable. It returns you to the start of the current phase, and a funded reset costs twice the challenge.</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>prime, flex-1-step</t>
+          <t>prime, flex-1-step, 1-step</t>
         </is>
       </c>
       <c r="F38" s="16" t="n"/>
@@ -4055,52 +4055,144 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>trading</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Minimum holding time</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>The August 2026 fee document requires a funded position to be held at least five minutes to count.</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
       <c r="E42" s="16" t="n"/>
       <c r="F42" s="16" t="n"/>
-      <c r="G42" s="16" t="n"/>
-      <c r="H42" s="16" t="n"/>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>funded</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>https://blueberryfunded.com/wp-content/uploads/2026/08/BBF-Trading-Evaluation-Outline-and-Fees-August-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>trading</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Risk Limiter</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>The risk team may place a trader under a 1% limit per trade idea, with a mandatory stop-loss on every order. The decision is theirs, announced by email, and it follows every account you hold.</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
       <c r="E43" s="16" t="n"/>
       <c r="F43" s="16" t="n"/>
       <c r="G43" s="16" t="n"/>
       <c r="H43" s="16" t="n"/>
       <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>https://help.blueberryfunded.com/en/articles/14051055-risk-limiter</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>trading</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Restricted countries</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>The help centre lists 16 countries, including the United States and Australia. The August 2026 fee document lists nine territories. The two official lists differ.</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>source_conflict</t>
+        </is>
+      </c>
       <c r="E44" s="16" t="n"/>
       <c r="F44" s="16" t="n"/>
       <c r="G44" s="16" t="n"/>
       <c r="H44" s="16" t="n"/>
       <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>https://help.blueberryfunded.com/en/articles/9550574-are-any-countries-restricted-from-purchasing-an-evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>payouts</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Termination without cause</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>Clause 18.2 of the terms reads: « The Company may terminate your use of the Services for any reason and without cause at any time. » Clause 18.4 lets the firm suspend an account instead, for a length it decides.</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
       <c r="E45" s="16" t="n"/>
       <c r="F45" s="16" t="n"/>
       <c r="G45" s="16" t="n"/>
       <c r="H45" s="16" t="n"/>
-      <c r="I45" s="16" t="n"/>
-      <c r="J45" s="16" t="n"/>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>https://blueberryfunded.com/wp-content/uploads/2024/08/BBF-Technology-Access-and-Trader-Assessment-Program-Terms-and-Conditions.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="n"/>
@@ -7749,7 +7841,9 @@
         </is>
       </c>
       <c r="H15" s="16" t="n"/>
-      <c r="I15" s="29" t="n"/>
+      <c r="I15" s="29" t="n">
+        <v>31</v>
+      </c>
       <c r="J15" s="29" t="n">
         <v>0</v>
       </c>
@@ -7783,7 +7877,7 @@
         </is>
       </c>
       <c r="E16" s="29" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="F16" s="16" t="n"/>
       <c r="G16" s="16" t="inlineStr">
@@ -7792,7 +7886,9 @@
         </is>
       </c>
       <c r="H16" s="16" t="n"/>
-      <c r="I16" s="29" t="n"/>
+      <c r="I16" s="29" t="n">
+        <v>58</v>
+      </c>
       <c r="J16" s="29" t="n">
         <v>0</v>
       </c>
@@ -7835,7 +7931,9 @@
         </is>
       </c>
       <c r="H17" s="16" t="n"/>
-      <c r="I17" s="29" t="n"/>
+      <c r="I17" s="29" t="n">
+        <v>116</v>
+      </c>
       <c r="J17" s="29" t="n">
         <v>0</v>
       </c>
@@ -7869,7 +7967,7 @@
         </is>
       </c>
       <c r="E18" s="29" t="n">
-        <v>302</v>
+        <v>302.5</v>
       </c>
       <c r="F18" s="16" t="n"/>
       <c r="G18" s="16" t="inlineStr">
@@ -7878,7 +7976,9 @@
         </is>
       </c>
       <c r="H18" s="16" t="n"/>
-      <c r="I18" s="29" t="n"/>
+      <c r="I18" s="29" t="n">
+        <v>211</v>
+      </c>
       <c r="J18" s="29" t="n">
         <v>0</v>
       </c>
@@ -7921,7 +8021,9 @@
         </is>
       </c>
       <c r="H19" s="16" t="n"/>
-      <c r="I19" s="29" t="n"/>
+      <c r="I19" s="29" t="n">
+        <v>424</v>
+      </c>
       <c r="J19" s="29" t="n">
         <v>0</v>
       </c>
@@ -7964,7 +8066,9 @@
         </is>
       </c>
       <c r="H20" s="16" t="n"/>
-      <c r="I20" s="29" t="n"/>
+      <c r="I20" s="29" t="n">
+        <v>847</v>
+      </c>
       <c r="J20" s="29" t="n">
         <v>0</v>
       </c>

--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -6306,7 +6306,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://tradelocker.com/favicon.ico</t>
+          <t>https://tradelocker.com/wp-content/uploads/2023/04/cropped-Icon-3-180x180.png</t>
         </is>
       </c>
     </row>

--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -6826,7 +6826,7 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>Funded from purchase, from $42.50</t>
+          <t>Funded from purchase, tightest rules</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">

--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1502,6 +1502,18 @@
       <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Seule une offre confirmed s'affiche : remise, code, Copy code et Claim deal. Vide ou needs_confirmation : la carte garde le plan, le prix public et Continue to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>accroche</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
         </is>
       </c>
     </row>

--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1514,6 +1514,30 @@
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>remise_campagne</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Taux d'une campagne a duree limitee, en %. Il remplace « remise » jusqu'a « campagne_fin », puis la fiche revient a « remise ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>campagne_fin</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
         </is>
       </c>
     </row>

--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1538,6 +1538,18 @@
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots pour ce que l'offre donne en plus du pourcentage (« +1 free reset »). Affiche en pastille sur la fiche et sur la carte /compare. Suit la campagne : il disparait avec elle.</t>
         </is>
       </c>
     </row>

--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -1511,6 +1511,11 @@
           <t>accroche</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Works on every account type, and it has no end date.</t>
+        </is>
+      </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
@@ -1545,6 +1550,11 @@
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>bonus</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>No expiry</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
@@ -2330,10 +2340,24 @@
       <c r="E6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
+      <c r="A7" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Public campaigns</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Prime only, dated</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Blueberry runs its own codes from time to time. They are limited to Prime accounts and to a deadline; SCANNED has neither limit and applies to every account type (confirmed by Blueberry support, 30 September 2026).</t>
+        </is>
+      </c>
       <c r="E7" s="16" t="n"/>
     </row>
     <row r="8">

--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -1552,11 +1552,6 @@
           <t>bonus</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No expiry</t>
-        </is>
-      </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
           <t>Deux ou trois mots pour ce que l'offre donne en plus du pourcentage (« +1 free reset »). Affiche en pastille sur la fiche et sur la carte /compare. Suit la campagne : il disparait avec elle.</t>

--- a/data/firms/blueberry-funded.xlsx
+++ b/data/firms/blueberry-funded.xlsx
@@ -17,15 +17,16 @@
     <sheet name="Phases" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="OptionsAchat" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Offre" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Conditions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Parcours" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Formation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ComptesApresReussite" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Couts" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Regles" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Verdict" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="FAQ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Listes" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet name="Campagnes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Conditions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Parcours" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Formation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ComptesApresReussite" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Couts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Regles" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Verdict" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="FAQ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Listes" sheetId="20" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1578,6 +1579,92 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>debut</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>remise</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO d'ouverture. Avant elle, la campagne n'existe nulle part.</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO de fermeture. Passee, la campagne disparait d'elle-meme.</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots, pour la pastille : « Day 4 · -60% TCP25 ».</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Une phrase : ce que l'offre donne, telle qu'elle s'affiche.</t>
+        </is>
+      </c>
+      <c r="E2" s="25" t="inlineStr">
+        <is>
+          <t>Taux pendant la fenetre, en %. Vide : le taux habituel de l'offre ne change pas.</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>confirmed pour s'afficher. Toute autre valeur la garde en reserve.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1673,7 +1760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1876,7 +1963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1986,7 +2073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2175,7 +2262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2417,7 +2504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -4512,7 +4599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -4817,7 +4904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -5062,7 +5149,573 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F2937"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Champ</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Valeur a remplir</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Exemple — FuturesElite, 7 sept. 2026</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Ou ca s'affiche dans le HTML · si vide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>blueberry-funded</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>futureselite</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Blueberry Funded</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>https://blueberryfunded.com/favicon.ico</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_score</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_review_count</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Nombre d'avis sous la note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_url</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/blueberryfunded.com</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/exemple.com</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>marches</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>cfd</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>futures</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Six ways to reach a simulated funded CFD account</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Four routes to a funded futures account</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Blueberry Funded belongs to the Blueberry Markets group and sells six routes: two instant-funding accounts and four evaluations, from $1,250 to $200,000. The rules are not shared across the range — drawdown, news window, weekend holding and payout conditions all depend on the route you pick.</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>presentation</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Blueberry Funded launched in August 2024. The contracting entity is Blueberry Markets (SVG) LLC, registered in Saint Vincent and the Grenadines under number 2090 LLC 2022, and the group behind it is the broker Blueberry Markets.
+Every account is simulated: no real capital is handed to the trader, and the rewards are paid on simulated profits.
+The catalogue holds 36 buyable combinations across six programs. Prime is the two-step route, and the most permissive one on concentration and position size. Flex pays 85% and gives 12% of static drawdown, in exchange for a 1% limit per trade idea, a five-minute news window and no weekend holding. The two Instant accounts skip the evaluation, with a trailing drawdown that locks at the starting balance.</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>« Founded ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>pays</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Saint Vincent and the Grenadines</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>« Country ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>ceo_fondateur</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Dean Hyde</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Christian Habibi</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>« CEO / Founder ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>actifs</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Forex, Indices, Metals, Energies, Crypto, Synthetic indices</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>(vide — non confirmees)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs_statut</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>plateformes</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>moyens_paiement</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Credit/Debit Card, Crypto</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>methodes_retrait</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Crypto, Rise, Transfer to a Blueberry Markets account</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Crypto, Riseworks</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>prestataire_retrait</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Rise</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>levier</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>levier_statut</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>styles_trading</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Day trading, Swing</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>(vide — absent du releve)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>meta_description</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>flux_donnees</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -5455,572 +6108,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F2937"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Champ</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Valeur a remplir</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Exemple — FuturesElite, 7 sept. 2026</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Ou ca s'affiche dans le HTML · si vide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>blueberry-funded</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>futureselite</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>nom</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Blueberry Funded</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>logo_url</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>https://blueberryfunded.com/favicon.ico</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_score</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_review_count</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="22" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Nombre d'avis sous la note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_url</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/blueberryfunded.com</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/exemple.com</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>marches</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>cfd</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>futures</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>titre</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Six ways to reach a simulated funded CFD account</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Four routes to a funded futures account</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Blueberry Funded belongs to the Blueberry Markets group and sells six routes: two instant-funding accounts and four evaluations, from $1,250 to $200,000. The rules are not shared across the range — drawdown, news window, weekend holding and payout conditions all depend on the route you pick.</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>presentation</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Blueberry Funded launched in August 2024. The contracting entity is Blueberry Markets (SVG) LLC, registered in Saint Vincent and the Grenadines under number 2090 LLC 2022, and the group behind it is the broker Blueberry Markets.
-Every account is simulated: no real capital is handed to the trader, and the rewards are paid on simulated profits.
-The catalogue holds 36 buyable combinations across six programs. Prime is the two-step route, and the most permissive one on concentration and position size. Flex pays 85% and gives 12% of static drawdown, in exchange for a 1% limit per trade idea, a five-minute news window and no weekend holding. The two Instant accounts skip the evaluation, with a trailing drawdown that locks at the starting balance.</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>« Founded ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Saint Vincent and the Grenadines</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>« Country ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>ceo_fondateur</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Dean Hyde</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Christian Habibi</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>actifs</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Forex, Indices, Metals, Energies, Crypto, Synthetic indices</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>(vide — non confirmees)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs_statut</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>plateformes</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>moyens_paiement</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Credit/Debit Card, Crypto</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>methodes_retrait</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Crypto, Rise, Transfer to a Blueberry Markets account</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Crypto, Riseworks</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>prestataire_retrait</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Rise</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>levier</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>N/A (futures contracts)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>levier_statut</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>styles_trading</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>Day trading, Swing</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>(vide — absent du releve)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>meta_description</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>flux_donnees</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
